--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/velo-it.xlsx
+++ b/output/velo-it.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
